--- a/doc/bhrn_npi.xlsx
+++ b/doc/bhrn_npi.xlsx
@@ -1028,6 +1028,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PAUL BONDS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2079,6 +2104,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SARAH COLVIN</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2989,6 +3039,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CAROLYN RICH</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4181,6 +4256,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AMY SLIVKOFF</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4480,6 +4580,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>DUSTY TAYLOR</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5390,6 +5515,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>JEWELY WALLACE</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5689,6 +5839,31 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>JENNIFER LESLIE</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6129,6 +6304,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>JAMIE LONG</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6992,6 +7192,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>TANYA COLLAZO</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7620,6 +7845,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>ADRIAN ABLE</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7637,6 +7887,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>ANDREW ERRAND</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8735,6 +9010,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>DONNA HOUGHTON</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9880,6 +10180,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>JAMIE SABINS</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -10226,6 +10551,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>AILEEN O'HOGAN</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -10948,6 +11298,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>SAMANTHA WRIGHT</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -11012,6 +11387,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>MICHELLE CRAFFORD</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -11029,6 +11429,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>MICHELLE CRAFFORD</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -11281,6 +11706,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>HEATHER FAIRBANKS</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -11298,6 +11748,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>REBECCA WHITELEY</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -12913,6 +13388,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>KYLE JOHANSEN</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -14451,6 +14951,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>JADA MARCUM</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -15079,6 +15604,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>TAMI PUTZIER</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -15707,6 +16257,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>MCKAYLAH ALLEN</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -15724,6 +16299,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>MCKAYLAH ALLEN</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -15741,6 +16341,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>MCKAYLAH ALLEN</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -15758,6 +16383,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>MCKAYLAH ALLEN</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -16245,6 +16895,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>RITA HAGER</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -16262,6 +16937,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>NATALIA NOVIKOFF</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -16749,6 +17449,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>KATRINA THIESSEN</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -16766,6 +17491,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>WENDY SANFORD</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -16971,6 +17721,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>KRISTINA WELLS FOWLER</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -18069,6 +18844,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>KOURTNIE MCKINNIS</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -18086,6 +18886,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>AARON LOPEZ</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -18197,6 +19022,31 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>JASON WILSON</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -21034,6 +21884,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>SHIRAM WORTHINGTON</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -21333,6 +22208,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>DEBORHA WOODS</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -22166,6 +23066,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>RICHARD NELSON</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -22606,6 +23531,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>ZACK MCCALLIE</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -23610,6 +24560,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>DEBORAH JANKE</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -24849,6 +25824,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>AMBER WALDROP</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -24866,6 +25866,31 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>JACKLYN RAYMOND</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -25541,6 +26566,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>JULIE PRITCHETT</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 971284825</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>971284825</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -26748,6 +27798,31 @@
       <c r="C591" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>MARGO GUAJARDO</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>213 NE 10TH ST NA MCMINNVILLE OR 97128</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>MCMINNVILLE</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>97128</t>
         </is>
       </c>
     </row>
